--- a/experiments/260223_ms/260224_sample_sheet_eric_ulrich.xlsx
+++ b/experiments/260223_ms/260224_sample_sheet_eric_ulrich.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="285">
   <si>
     <t xml:space="preserve">At
 Succinate</t>
@@ -886,10 +886,16 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">injection_number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">batch</t>
+    <t xml:space="preserve">in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t</t>
   </si>
 </sst>
 </file>
@@ -5239,15 +5245,15 @@
   <dimension ref="A1:I135"/>
   <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="16.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="6.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="2.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="4.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="5.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="34.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="3.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="34.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="8.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="10.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="8.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="8" width="9.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="8" width="5.65"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5261,7 +5267,7 @@
         <v>32</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>33</v>
+        <v>283</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>31</v>
@@ -5276,7 +5282,7 @@
         <v>36</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>37</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
